--- a/datos/formato_import_categorias.xlsx
+++ b/datos/formato_import_categorias.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Clarence\Documents\Playwright\Inventario\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Clarence\Documents\GitHub\erpmarketrest-qa\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A00B83A-2F47-4CDE-8F0E-5D1EE56EA2A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0E53105-65DB-479D-99C7-ACD421923B1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
     <t>NOMBRE</t>
   </si>
   <si>
-    <t>CATEGORIA10023</t>
+    <t>CATEGORIA10024</t>
   </si>
 </sst>
 </file>
